--- a/cosmos-graph/interim/Codelist_Coverage.xlsx
+++ b/cosmos-graph/interim/Codelist_Coverage.xlsx
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-02 15:19</t>
+          <t>Generated: 2026-06-12 21:33</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         <v>28</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
@@ -7421,10 +7421,10 @@
         <v>100</v>
       </c>
       <c r="F158" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G158" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H158" s="6" t="n">
         <v>0</v>
@@ -8471,20 +8471,20 @@
         <v>7</v>
       </c>
       <c r="F183" s="6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G183" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I183" s="6" t="n">
         <v>29</v>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>EC; EX; MK; RP; SR; TU; UR; VS</t>
+          <t>EC; EX; MK; PR; RP; SR; TU; UR; VS</t>
         </is>
       </c>
     </row>
@@ -10944,13 +10944,13 @@
         <v>2</v>
       </c>
       <c r="G242" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H242" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I242" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
@@ -11403,10 +11403,10 @@
         <v>129</v>
       </c>
       <c r="F253" s="6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G253" s="6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H253" s="6" t="n">
         <v>295</v>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
-          <t>BE; IS; LB; MB; MI</t>
+          <t>BE; IS; LB; MB; MI; UR</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
         <v>525</v>
       </c>
       <c r="G287" s="6" t="n">
-        <v>429</v>
+        <v>245</v>
       </c>
       <c r="H287" s="6" t="n">
         <v>396</v>
@@ -13070,7 +13070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G396"/>
+  <dimension ref="A1:G398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14963,10 +14963,10 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>0</v>
@@ -18211,10 +18211,10 @@
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E177" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0</v>
@@ -19019,20 +19019,20 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E205" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G205" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -19048,20 +19048,20 @@
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E206" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G206" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207">
@@ -19077,11 +19077,11 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D207" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E207" s="6" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208">
@@ -19106,20 +19106,20 @@
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D208" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E208" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G208" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209">
@@ -19135,17 +19135,17 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D209" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E209" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F209" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G209" s="6" t="n">
         <v>0</v>
@@ -19154,27 +19154,27 @@
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>C67154</t>
+          <t>C99073</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>LBTEST</t>
+          <t>LAT</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D210" s="6" t="n">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="E210" s="6" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>0</v>
@@ -19183,12 +19183,12 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>C65047</t>
+          <t>C67154</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>LBTESTCD</t>
+          <t>LBTEST</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -19212,30 +19212,30 @@
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>C74456</t>
+          <t>C65047</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>LOC</t>
+          <t>LBTESTCD</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D212" s="6" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G212" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D213" s="6" t="n">
@@ -19261,10 +19261,10 @@
         <v>0</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -19280,17 +19280,17 @@
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D214" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>1</v>
@@ -19309,20 +19309,20 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D215" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E215" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G215" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -19338,17 +19338,17 @@
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="D216" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E216" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>0</v>
@@ -19367,20 +19367,20 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D217" s="6" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="E217" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G217" s="6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -19396,20 +19396,20 @@
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D218" s="6" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E218" s="6" t="n">
         <v>3</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G218" s="6" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219">
@@ -19425,20 +19425,20 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E219" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G219" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -19454,20 +19454,20 @@
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D220" s="6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="221">
@@ -19483,20 +19483,20 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D221" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E221" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -19512,11 +19512,11 @@
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D222" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E222" s="6" t="n">
         <v>0</v>
@@ -19525,7 +19525,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223">
@@ -19541,20 +19541,20 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D223" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E223" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G223" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224">
@@ -19570,17 +19570,17 @@
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>0</v>
@@ -19589,27 +19589,27 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>C174225</t>
+          <t>C74456</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>MBFTSDTL</t>
+          <t>LOC</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D225" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E225" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F225" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G225" s="6" t="n">
         <v>0</v>
@@ -19618,12 +19618,12 @@
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>C120528</t>
+          <t>C174225</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>MBTEST</t>
+          <t>MBFTSDTL</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
@@ -19647,12 +19647,12 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>C120527</t>
+          <t>C120528</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>MBTESTCD</t>
+          <t>MBTEST</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
@@ -19676,27 +19676,27 @@
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>C96777</t>
+          <t>C120527</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>MEDEVAL</t>
+          <t>MBTESTCD</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="D228" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E228" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>0</v>
@@ -19715,17 +19715,17 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D229" s="6" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E229" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F229" s="6" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G229" s="6" t="n">
         <v>0</v>
@@ -19744,17 +19744,17 @@
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D230" s="6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E230" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>0</v>
@@ -19773,17 +19773,17 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D231" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E231" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F231" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G231" s="6" t="n">
         <v>0</v>
@@ -19792,27 +19792,27 @@
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>C85492</t>
+          <t>C96777</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>METHOD</t>
+          <t>MEDEVAL</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D232" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E232" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F232" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>0</v>
@@ -19831,17 +19831,17 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="D233" s="6" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E233" s="6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F233" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G233" s="6" t="n">
         <v>0</v>
@@ -19860,17 +19860,17 @@
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D234" s="6" t="n">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="E234" s="6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F234" s="6" t="n">
-        <v>290</v>
+        <v>6</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>0</v>
@@ -19889,20 +19889,20 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D235" s="6" t="n">
-        <v>6</v>
+        <v>290</v>
       </c>
       <c r="E235" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F235" s="6" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="G235" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -19918,20 +19918,20 @@
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D236" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -19947,17 +19947,17 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="D237" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E237" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F237" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" s="6" t="n">
         <v>0</v>
@@ -19976,20 +19976,20 @@
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D238" s="6" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E238" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F238" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G238" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -20005,20 +20005,20 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D239" s="6" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E239" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F239" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G239" s="6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240">
@@ -20034,20 +20034,20 @@
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D240" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E240" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G240" s="6" t="n">
         <v>9</v>
-      </c>
-      <c r="E240" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F240" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G240" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -20063,17 +20063,17 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D241" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E241" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F241" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G241" s="6" t="n">
         <v>0</v>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D242" s="6" t="n">
@@ -20102,10 +20102,10 @@
         <v>0</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G242" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -20121,36 +20121,36 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D243" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E243" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F243" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G243" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>C124301</t>
+          <t>C85492</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>MHEDTTYP</t>
+          <t>METHOD</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D244" s="6" t="n">
@@ -20169,24 +20169,24 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>C85491</t>
+          <t>C124301</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>MICROORG</t>
+          <t>MHEDTTYP</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="D245" s="6" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="E245" s="6" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="F245" s="6" t="n">
         <v>0</v>
@@ -20198,24 +20198,24 @@
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>C125922</t>
+          <t>C85491</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>MIFTSDTL</t>
+          <t>MICROORG</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D246" s="6" t="n">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="E246" s="6" t="n">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="F246" s="6" t="n">
         <v>0</v>
@@ -20227,12 +20227,12 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>C132262</t>
+          <t>C125922</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>MITS</t>
+          <t>MIFTSDTL</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
@@ -20256,12 +20256,12 @@
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>C132263</t>
+          <t>C132262</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>MITSCD</t>
+          <t>MITS</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
@@ -20285,27 +20285,27 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>C181165</t>
+          <t>C132263</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>MODDLV</t>
+          <t>MITSCD</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D249" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E249" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F249" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G249" s="6" t="n">
         <v>0</v>
@@ -20314,12 +20314,12 @@
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>C185847</t>
+          <t>C181165</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>MPSTATRS</t>
+          <t>MODDLV</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
@@ -20334,50 +20334,50 @@
         <v>0</v>
       </c>
       <c r="F250" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>C127270</t>
+          <t>C185847</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>MUSCTS</t>
+          <t>MPSTATRS</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D251" s="6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E251" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F251" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G251" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>C127269</t>
+          <t>C127270</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>MUSCTSCD</t>
+          <t>MUSCTS</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr">
@@ -20401,41 +20401,41 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>C190893</t>
+          <t>C127269</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>MVAI101OR</t>
+          <t>MUSCTSCD</t>
         </is>
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D253" s="6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E253" s="6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G253" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>C190894</t>
+          <t>C190893</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>MVAI101STR</t>
+          <t>MVAI101OR</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
@@ -20459,12 +20459,12 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>C190895</t>
+          <t>C190894</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>MVAI102OR</t>
+          <t>MVAI101STR</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
@@ -20488,12 +20488,12 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>C190896</t>
+          <t>C190895</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>MVAI102STR</t>
+          <t>MVAI102OR</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr">
@@ -20517,12 +20517,12 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>C190897</t>
+          <t>C190896</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>MVAI103OR</t>
+          <t>MVAI102STR</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
@@ -20546,12 +20546,12 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>C190898</t>
+          <t>C190897</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>MVAI103STR</t>
+          <t>MVAI103OR</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
@@ -20575,12 +20575,12 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>C190899</t>
+          <t>C190898</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>MVAI104OR</t>
+          <t>MVAI103STR</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr">
@@ -20604,12 +20604,12 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>C190900</t>
+          <t>C190899</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>MVAI104STR</t>
+          <t>MVAI104OR</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
@@ -20633,12 +20633,12 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>C190901</t>
+          <t>C190900</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>MVAI105OR</t>
+          <t>MVAI104STR</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
@@ -20662,12 +20662,12 @@
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>C190902</t>
+          <t>C190901</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>MVAI105STR</t>
+          <t>MVAI105OR</t>
         </is>
       </c>
       <c r="C262" s="6" t="inlineStr">
@@ -20691,12 +20691,12 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>C190930</t>
+          <t>C190902</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>MVAI1TC</t>
+          <t>MVAI105STR</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
@@ -20705,27 +20705,27 @@
         </is>
       </c>
       <c r="D263" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E263" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F263" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G263" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>C190929</t>
+          <t>C190930</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>MVAI1TN</t>
+          <t>MVAI1TC</t>
         </is>
       </c>
       <c r="C264" s="6" t="inlineStr">
@@ -20749,59 +20749,59 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>C66727</t>
+          <t>C190929</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>NCOMPLT</t>
+          <t>MVAI1TN</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D265" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E265" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F265" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>C66789</t>
+          <t>C66727</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>NCOMPLT</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="D266" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E266" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F266" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G266" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -20817,17 +20817,17 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="D267" s="6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E267" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F267" s="6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G267" s="6" t="n">
         <v>0</v>
@@ -20836,59 +20836,59 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>C101834</t>
+          <t>C66789</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>NORMABNM</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D268" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E268" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G268" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>C66742</t>
+          <t>C101834</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NORMABNM</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D269" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E269" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F269" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G269" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -20904,20 +20904,20 @@
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D270" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E270" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G270" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -20933,20 +20933,20 @@
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D271" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E271" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F271" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G271" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -20962,17 +20962,17 @@
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="D272" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E272" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>0</v>
@@ -20991,17 +20991,17 @@
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D273" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E273" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F273" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G273" s="6" t="n">
         <v>0</v>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D274" s="6" t="n">
@@ -21049,17 +21049,17 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D275" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E275" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F275" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G275" s="6" t="n">
         <v>0</v>
@@ -21078,17 +21078,17 @@
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="D276" s="6" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="E276" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>0</v>
@@ -21107,17 +21107,17 @@
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D277" s="6" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="E277" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F277" s="6" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="G277" s="6" t="n">
         <v>0</v>
@@ -21136,17 +21136,17 @@
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="D278" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E278" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>0</v>
@@ -21165,20 +21165,20 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D279" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E279" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F279" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G279" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -21194,20 +21194,20 @@
       </c>
       <c r="C280" s="6" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D280" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E280" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G280" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -21223,20 +21223,20 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D281" s="6" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E281" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F281" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G281" s="6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -21252,20 +21252,20 @@
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D282" s="6" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E282" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F282" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G282" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="283">
@@ -21281,17 +21281,17 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D283" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E283" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F283" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G283" s="6" t="n">
         <v>0</v>
@@ -21310,17 +21310,17 @@
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D284" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E284" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F284" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>0</v>
@@ -21339,17 +21339,17 @@
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D285" s="6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E285" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F285" s="6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G285" s="6" t="n">
         <v>0</v>
@@ -21368,17 +21368,17 @@
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D286" s="6" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E286" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>0</v>
@@ -21397,17 +21397,17 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D287" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E287" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F287" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G287" s="6" t="n">
         <v>0</v>
@@ -21416,41 +21416,41 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>C127259</t>
+          <t>C66742</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>OBSSMO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D288" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E288" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G288" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>C127260</t>
+          <t>C127259</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>OBSSSM</t>
+          <t>OBSSMO</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
@@ -21474,12 +21474,12 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>C127261</t>
+          <t>C127260</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>OBSSTP</t>
+          <t>OBSSSM</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr">
@@ -21503,41 +21503,41 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>C124298</t>
+          <t>C127261</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>ONCRSCAT</t>
+          <t>OBSSTP</t>
         </is>
       </c>
       <c r="C291" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D291" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E291" s="6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F291" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G291" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>C96785</t>
+          <t>C124298</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>ONCRSR</t>
+          <t>ONCRSCAT</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr">
@@ -21546,13 +21546,13 @@
         </is>
       </c>
       <c r="D292" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E292" s="6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>0</v>
@@ -21561,12 +21561,12 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>C96781</t>
+          <t>C96785</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>ONCRTS</t>
+          <t>ONCRSR</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
@@ -21575,13 +21575,13 @@
         </is>
       </c>
       <c r="D293" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E293" s="6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F293" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G293" s="6" t="n">
         <v>0</v>
@@ -21590,12 +21590,12 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>C96782</t>
+          <t>C96781</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>ONCRTSCD</t>
+          <t>ONCRTS</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
@@ -21619,24 +21619,24 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>C150811</t>
+          <t>C96782</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>OTHEVENT</t>
+          <t>ONCRTSCD</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D295" s="6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E295" s="6" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F295" s="6" t="n">
         <v>0</v>
@@ -21648,50 +21648,50 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>C66768</t>
+          <t>C150811</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>OTHEVENT</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="D296" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E296" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F296" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G296" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>C71148</t>
+          <t>C66768</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>POSITION</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D297" s="6" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E297" s="6" t="n">
         <v>0</v>
@@ -21700,7 +21700,7 @@
         <v>0</v>
       </c>
       <c r="G297" s="6" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -21716,101 +21716,101 @@
       </c>
       <c r="C298" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D298" s="6" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E298" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F298" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G298" s="6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>C101858</t>
+          <t>C71148</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>PROCEDUR</t>
+          <t>POSITION</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D299" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E299" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F299" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G299" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>C114118</t>
+          <t>C101858</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>PROTMLST</t>
+          <t>PROCEDUR</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
         <is>
-          <t>DS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D300" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E300" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F300" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>C158113</t>
+          <t>C114118</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>QRSMTHOD</t>
+          <t>PROTMLST</t>
         </is>
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>DS</t>
         </is>
       </c>
       <c r="D301" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E301" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F301" s="6" t="n">
         <v>0</v>
@@ -21822,12 +21822,12 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>C100129</t>
+          <t>C158113</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>QSCAT</t>
+          <t>QRSMTHOD</t>
         </is>
       </c>
       <c r="C302" s="6" t="inlineStr">
@@ -21836,10 +21836,10 @@
         </is>
       </c>
       <c r="D302" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E302" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F302" s="6" t="n">
         <v>0</v>
@@ -21851,27 +21851,27 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>C74457</t>
+          <t>C100129</t>
         </is>
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>QSCAT</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="D303" s="6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E303" s="6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F303" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G303" s="6" t="n">
         <v>0</v>
@@ -21880,27 +21880,27 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>C111107</t>
+          <t>C74457</t>
         </is>
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>RETEST</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="C304" s="6" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D304" s="6" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="E304" s="6" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F304" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>0</v>
@@ -21909,12 +21909,12 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>C111106</t>
+          <t>C111107</t>
         </is>
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>RETESTCD</t>
+          <t>RETEST</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
@@ -21938,30 +21938,30 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>C66729</t>
+          <t>C111106</t>
         </is>
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>RETESTCD</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D306" s="6" t="n">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="E306" s="6" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F306" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G306" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -21977,20 +21977,20 @@
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D307" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E307" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G307" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
@@ -22006,14 +22006,14 @@
       </c>
       <c r="C308" s="6" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D308" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E308" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" s="6" t="n">
         <v>0</v>
@@ -22035,7 +22035,7 @@
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D309" s="6" t="n">
@@ -22054,41 +22054,41 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>C106478</t>
+          <t>C66729</t>
         </is>
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>RPTEST</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="C310" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D310" s="6" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="E310" s="6" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F310" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G310" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>C106479</t>
+          <t>C106478</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>RPTESTCD</t>
+          <t>RPTEST</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
@@ -22112,46 +22112,46 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>C101848</t>
+          <t>C106479</t>
         </is>
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>RSKASMT</t>
+          <t>RPTESTCD</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D312" s="6" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="E312" s="6" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F312" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G312" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>C190903</t>
+          <t>C101848</t>
         </is>
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>RUTG0101OR</t>
+          <t>RSKASMT</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D313" s="6" t="n">
@@ -22170,12 +22170,12 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>C190904</t>
+          <t>C190903</t>
         </is>
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>RUTG0101STR</t>
+          <t>RUTG0101OR</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
@@ -22199,12 +22199,12 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>C190932</t>
+          <t>C190904</t>
         </is>
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>RUTG01TC</t>
+          <t>RUTG0101STR</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
@@ -22216,24 +22216,24 @@
         <v>1</v>
       </c>
       <c r="E315" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F315" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G315" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>C190931</t>
+          <t>C190932</t>
         </is>
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>RUTG01TN</t>
+          <t>RUTG01TC</t>
         </is>
       </c>
       <c r="C316" s="6" t="inlineStr">
@@ -22257,41 +22257,41 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>C103330</t>
+          <t>C190931</t>
         </is>
       </c>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>SCTEST</t>
+          <t>RUTG01TN</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D317" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E317" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F317" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G317" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>C74559</t>
+          <t>C103330</t>
         </is>
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>SCTESTCD</t>
+          <t>SCTEST</t>
         </is>
       </c>
       <c r="C318" s="6" t="inlineStr">
@@ -22315,41 +22315,41 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>C189266</t>
+          <t>C74559</t>
         </is>
       </c>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>SDTMDVRS</t>
+          <t>SCTESTCD</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="D319" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E319" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F319" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G319" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>C160924</t>
+          <t>C189266</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>SDTMIGRS</t>
+          <t>SDTMDVRS</t>
         </is>
       </c>
       <c r="C320" s="6" t="inlineStr">
@@ -22373,12 +22373,12 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>C160923</t>
+          <t>C160924</t>
         </is>
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>SDTMVRS</t>
+          <t>SDTMIGRS</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
@@ -22402,17 +22402,17 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>C127262</t>
+          <t>C160923</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>SETTING</t>
+          <t>SDTMVRS</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D322" s="6" t="n">
@@ -22431,17 +22431,17 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>C66731</t>
+          <t>C127262</t>
         </is>
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>SETTING</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="D323" s="6" t="n">
@@ -22451,26 +22451,26 @@
         <v>0</v>
       </c>
       <c r="F323" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G323" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>C66732</t>
+          <t>C66731</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>SEXPOP</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C324" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D324" s="6" t="n">
@@ -22480,50 +22480,50 @@
         <v>0</v>
       </c>
       <c r="F324" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>C115388</t>
+          <t>C66732</t>
         </is>
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>SIXMW1TC</t>
+          <t>SEXPOP</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D325" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E325" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F325" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G325" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>C115387</t>
+          <t>C115388</t>
         </is>
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>SIXMW1TN</t>
+          <t>SIXMW1TC</t>
         </is>
       </c>
       <c r="C326" s="6" t="inlineStr">
@@ -22547,27 +22547,27 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>C66733</t>
+          <t>C115387</t>
         </is>
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>SIZE</t>
+          <t>SIXMW1TN</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="D327" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E327" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F327" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G327" s="6" t="n">
         <v>0</v>
@@ -22586,49 +22586,49 @@
       </c>
       <c r="C328" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D328" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E328" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F328" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G328" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>C78734</t>
+          <t>C66733</t>
         </is>
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>SPECTYPE</t>
+          <t>SIZE</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D329" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E329" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F329" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -22644,20 +22644,20 @@
       </c>
       <c r="C330" s="6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="D330" s="6" t="n">
-        <v>290</v>
+        <v>7</v>
       </c>
       <c r="E330" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F330" s="6" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G330" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331">
@@ -22673,17 +22673,17 @@
       </c>
       <c r="C331" s="6" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D331" s="6" t="n">
-        <v>146</v>
+        <v>290</v>
       </c>
       <c r="E331" s="6" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="F331" s="6" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="G331" s="6" t="n">
         <v>0</v>
@@ -22702,17 +22702,17 @@
       </c>
       <c r="C332" s="6" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D332" s="6" t="n">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="E332" s="6" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>0</v>
@@ -22731,17 +22731,17 @@
       </c>
       <c r="C333" s="6" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="D333" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E333" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F333" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G333" s="6" t="n">
         <v>0</v>
@@ -22750,24 +22750,24 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>C112023</t>
+          <t>C78734</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>SRTEST</t>
+          <t>SPECTYPE</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D334" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E334" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F334" s="6" t="n">
         <v>0</v>
@@ -22779,24 +22779,24 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>C112024</t>
+          <t>C78734</t>
         </is>
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>SRTESTCD</t>
+          <t>SPECTYPE</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D335" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E335" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F335" s="6" t="n">
         <v>0</v>
@@ -22808,27 +22808,27 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>C66728</t>
+          <t>C112023</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>STENRF</t>
+          <t>SRTEST</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D336" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E336" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F336" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G336" s="6" t="n">
         <v>0</v>
@@ -22837,30 +22837,30 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>C66728</t>
+          <t>C112024</t>
         </is>
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>STENRF</t>
+          <t>SRTESTCD</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D337" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E337" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F337" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -22876,20 +22876,20 @@
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D338" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E338" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F338" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G338" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -22905,94 +22905,94 @@
       </c>
       <c r="C339" s="6" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D339" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E339" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F339" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G339" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>C99077</t>
+          <t>C66728</t>
         </is>
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>STYPE</t>
+          <t>STENRF</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="D340" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E340" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F340" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G340" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>C181176</t>
+          <t>C66728</t>
         </is>
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>SYMTYPGF</t>
+          <t>STENRF</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D341" s="6" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E341" s="6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F341" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G341" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>C193257</t>
+          <t>C99077</t>
         </is>
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>TANN0101OR</t>
+          <t>STYPE</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D342" s="6" t="n">
@@ -23011,41 +23011,41 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>C193258</t>
+          <t>C181176</t>
         </is>
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>TANN0101STR</t>
+          <t>SYMTYPGF</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D343" s="6" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E343" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F343" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G343" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>C193259</t>
+          <t>C193257</t>
         </is>
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>TANN0102OR</t>
+          <t>TANN0101OR</t>
         </is>
       </c>
       <c r="C344" s="6" t="inlineStr">
@@ -23069,12 +23069,12 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>C193260</t>
+          <t>C193258</t>
         </is>
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>TANN0102STR</t>
+          <t>TANN0101STR</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
@@ -23098,12 +23098,12 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>C124664</t>
+          <t>C193259</t>
         </is>
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>TANN01TC</t>
+          <t>TANN0102OR</t>
         </is>
       </c>
       <c r="C346" s="6" t="inlineStr">
@@ -23112,27 +23112,27 @@
         </is>
       </c>
       <c r="D346" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E346" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F346" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G346" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>C124663</t>
+          <t>C193260</t>
         </is>
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>TANN01TN</t>
+          <t>TANN0102STR</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
@@ -23141,27 +23141,27 @@
         </is>
       </c>
       <c r="D347" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E347" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F347" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G347" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>C193261</t>
+          <t>C124664</t>
         </is>
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>TANN0201OR</t>
+          <t>TANN01TC</t>
         </is>
       </c>
       <c r="C348" s="6" t="inlineStr">
@@ -23170,27 +23170,27 @@
         </is>
       </c>
       <c r="D348" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E348" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F348" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G348" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>C193262</t>
+          <t>C124663</t>
         </is>
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>TANN0201STR</t>
+          <t>TANN01TN</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
@@ -23199,27 +23199,27 @@
         </is>
       </c>
       <c r="D349" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F349" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G349" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>C193263</t>
+          <t>C193261</t>
         </is>
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>TANN0202OR</t>
+          <t>TANN0201OR</t>
         </is>
       </c>
       <c r="C350" s="6" t="inlineStr">
@@ -23243,12 +23243,12 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>C193264</t>
+          <t>C193262</t>
         </is>
       </c>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>TANN0202STR</t>
+          <t>TANN0201STR</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
@@ -23272,12 +23272,12 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>C124662</t>
+          <t>C193263</t>
         </is>
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>TANN02TC</t>
+          <t>TANN0202OR</t>
         </is>
       </c>
       <c r="C352" s="6" t="inlineStr">
@@ -23286,27 +23286,27 @@
         </is>
       </c>
       <c r="D352" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E352" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F352" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G352" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>C124661</t>
+          <t>C193264</t>
         </is>
       </c>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>TANN02TN</t>
+          <t>TANN0202STR</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
@@ -23315,85 +23315,85 @@
         </is>
       </c>
       <c r="D353" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E353" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F353" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G353" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>C66735</t>
+          <t>C124662</t>
         </is>
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>TBLIND</t>
+          <t>TANN02TC</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D354" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E354" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F354" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G354" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>C66785</t>
+          <t>C124661</t>
         </is>
       </c>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>TCNTRL</t>
+          <t>TANN02TN</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D355" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E355" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F355" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G355" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>C66736</t>
+          <t>C66735</t>
         </is>
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>TINDTP</t>
+          <t>TBLIND</t>
         </is>
       </c>
       <c r="C356" s="6" t="inlineStr">
@@ -23417,12 +23417,12 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>C66737</t>
+          <t>C66785</t>
         </is>
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>TPHASE</t>
+          <t>TCNTRL</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
@@ -23446,70 +23446,70 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>C124309</t>
+          <t>C66736</t>
         </is>
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>TRPROPRS</t>
+          <t>TINDTP</t>
         </is>
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D358" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E358" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F358" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G358" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>C96778</t>
+          <t>C66737</t>
         </is>
       </c>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>TRTEST</t>
+          <t>TPHASE</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D359" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E359" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F359" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G359" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>C96779</t>
+          <t>C124309</t>
         </is>
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>TRTESTCD</t>
+          <t>TRPROPRS</t>
         </is>
       </c>
       <c r="C360" s="6" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="D360" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E360" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F360" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G360" s="6" t="n">
         <v>0</v>
@@ -23533,27 +23533,27 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>C124307</t>
+          <t>C96778</t>
         </is>
       </c>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>TRTINTNT</t>
+          <t>TRTEST</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D361" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E361" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F361" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G361" s="6" t="n">
         <v>0</v>
@@ -23562,27 +23562,27 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>C124307</t>
+          <t>C96779</t>
         </is>
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>TRTINTNT</t>
+          <t>TRTESTCD</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D362" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E362" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F362" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G362" s="6" t="n">
         <v>0</v>
@@ -23591,12 +23591,12 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>C124308</t>
+          <t>C124307</t>
         </is>
       </c>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>TRTSET</t>
+          <t>TRTINTNT</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
@@ -23620,12 +23620,12 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>C124308</t>
+          <t>C124307</t>
         </is>
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>TRTSET</t>
+          <t>TRTINTNT</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
@@ -23649,27 +23649,27 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>C67152</t>
+          <t>C124308</t>
         </is>
       </c>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>TSPARM</t>
+          <t>TRTSET</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D365" s="6" t="n">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="E365" s="6" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F365" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" s="6" t="n">
         <v>0</v>
@@ -23678,27 +23678,27 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>C66738</t>
+          <t>C124308</t>
         </is>
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>TSPARMCD</t>
+          <t>TRTSET</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D366" s="6" t="n">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="E366" s="6" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F366" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G366" s="6" t="n">
         <v>0</v>
@@ -23707,27 +23707,27 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>C181170</t>
+          <t>C67152</t>
         </is>
       </c>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>TSTOPOBJ</t>
+          <t>TSPARM</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D367" s="6" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="E367" s="6" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F367" s="6" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G367" s="6" t="n">
         <v>0</v>
@@ -23736,12 +23736,12 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>C66739</t>
+          <t>C66738</t>
         </is>
       </c>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>TTYPE</t>
+          <t>TSPARMCD</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
@@ -23750,42 +23750,42 @@
         </is>
       </c>
       <c r="D368" s="6" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="E368" s="6" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="F368" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G368" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>C123650</t>
+          <t>C181170</t>
         </is>
       </c>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>TUIDRS</t>
+          <t>TSTOPOBJ</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D369" s="6" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E369" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F369" s="6" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="G369" s="6" t="n">
         <v>0</v>
@@ -23794,41 +23794,41 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>C96783</t>
+          <t>C66739</t>
         </is>
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>TUTEST</t>
+          <t>TTYPE</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D370" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E370" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F370" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G370" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>C96784</t>
+          <t>C123650</t>
         </is>
       </c>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>TUTESTCD</t>
+          <t>TUIDRS</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
@@ -23837,13 +23837,13 @@
         </is>
       </c>
       <c r="D371" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E371" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F371" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G371" s="6" t="n">
         <v>0</v>
@@ -23852,59 +23852,59 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C96783</t>
         </is>
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TUTEST</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D372" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E372" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F372" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G372" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>C71620</t>
+          <t>C96784</t>
         </is>
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TUTESTCD</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="D373" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E373" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F373" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G373" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -23920,20 +23920,20 @@
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D374" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E374" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F374" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G374" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="375">
@@ -23949,14 +23949,14 @@
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D375" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E375" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F375" s="6" t="n">
         <v>0</v>
@@ -23978,17 +23978,17 @@
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D376" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E376" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F376" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G376" s="6" t="n">
         <v>0</v>
@@ -24007,20 +24007,20 @@
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D377" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E377" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F377" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G377" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -24036,17 +24036,17 @@
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="D378" s="6" t="n">
-        <v>185</v>
+        <v>6</v>
       </c>
       <c r="E378" s="6" t="n">
-        <v>185</v>
+        <v>6</v>
       </c>
       <c r="F378" s="6" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="G378" s="6" t="n">
         <v>0</v>
@@ -24065,20 +24065,20 @@
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="D379" s="6" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="E379" s="6" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="F379" s="6" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G379" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -24094,17 +24094,17 @@
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="D380" s="6" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="E380" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F380" s="6" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="G380" s="6" t="n">
         <v>0</v>
@@ -24123,20 +24123,20 @@
       </c>
       <c r="C381" s="6" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D381" s="6" t="n">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="E381" s="6" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="F381" s="6" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="G381" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -24152,17 +24152,17 @@
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="D382" s="6" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="E382" s="6" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="F382" s="6" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G382" s="6" t="n">
         <v>0</v>
@@ -24181,17 +24181,17 @@
       </c>
       <c r="C383" s="6" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D383" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E383" s="6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F383" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G383" s="6" t="n">
         <v>0</v>
@@ -24210,17 +24210,17 @@
       </c>
       <c r="C384" s="6" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D384" s="6" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="E384" s="6" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F384" s="6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G384" s="6" t="n">
         <v>0</v>
@@ -24239,17 +24239,17 @@
       </c>
       <c r="C385" s="6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="D385" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E385" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F385" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G385" s="6" t="n">
         <v>0</v>
@@ -24268,17 +24268,17 @@
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="D386" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E386" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F386" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G386" s="6" t="n">
         <v>0</v>
@@ -24297,20 +24297,20 @@
       </c>
       <c r="C387" s="6" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="D387" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E387" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F387" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G387" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -24326,17 +24326,17 @@
       </c>
       <c r="C388" s="6" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="D388" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E388" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F388" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G388" s="6" t="n">
         <v>0</v>
@@ -24355,20 +24355,20 @@
       </c>
       <c r="C389" s="6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="D389" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E389" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F389" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G389" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390">
@@ -24384,17 +24384,17 @@
       </c>
       <c r="C390" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D390" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E390" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F390" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G390" s="6" t="n">
         <v>0</v>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="C391" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="D391" s="6" t="n">
@@ -24423,21 +24423,21 @@
         <v>0</v>
       </c>
       <c r="F391" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G391" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>C129941</t>
+          <t>C71620</t>
         </is>
       </c>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>URNSTS</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
@@ -24446,13 +24446,13 @@
         </is>
       </c>
       <c r="D392" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E392" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F392" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G392" s="6" t="n">
         <v>0</v>
@@ -24461,27 +24461,27 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>C129942</t>
+          <t>C71620</t>
         </is>
       </c>
       <c r="B393" s="6" t="inlineStr">
         <is>
-          <t>URNSTSCD</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>UR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D393" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E393" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F393" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G393" s="6" t="n">
         <v>0</v>
@@ -24490,53 +24490,53 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>C66770</t>
+          <t>C129941</t>
         </is>
       </c>
       <c r="B394" s="6" t="inlineStr">
         <is>
-          <t>VSRESU</t>
+          <t>URNSTS</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D394" s="6" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="E394" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F394" s="6" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G394" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>C67153</t>
+          <t>C129942</t>
         </is>
       </c>
       <c r="B395" s="6" t="inlineStr">
         <is>
-          <t>VSTEST</t>
+          <t>URNSTSCD</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>UR</t>
         </is>
       </c>
       <c r="D395" s="6" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="E395" s="6" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="F395" s="6" t="n">
         <v>0</v>
@@ -24548,29 +24548,87 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
+          <t>C66770</t>
+        </is>
+      </c>
+      <c r="B396" s="6" t="inlineStr">
+        <is>
+          <t>VSRESU</t>
+        </is>
+      </c>
+      <c r="C396" s="6" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D396" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E396" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F396" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G396" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr">
+        <is>
+          <t>C67153</t>
+        </is>
+      </c>
+      <c r="B397" s="6" t="inlineStr">
+        <is>
+          <t>VSTEST</t>
+        </is>
+      </c>
+      <c r="C397" s="6" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D397" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E397" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F397" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr">
+        <is>
           <t>C66741</t>
         </is>
       </c>
-      <c r="B396" s="6" t="inlineStr">
+      <c r="B398" s="6" t="inlineStr">
         <is>
           <t>VSTESTCD</t>
         </is>
       </c>
-      <c r="C396" s="6" t="inlineStr">
+      <c r="C398" s="6" t="inlineStr">
         <is>
           <t>VS</t>
         </is>
       </c>
-      <c r="D396" s="6" t="n">
+      <c r="D398" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="E396" s="6" t="n">
+      <c r="E398" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="F396" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G396" s="6" t="n">
+      <c r="F398" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" s="6" t="n">
         <v>0</v>
       </c>
     </row>
